--- a/документы/замеры-объектов/2026-08-02-Евгений-замеры-санузлы-коридор-лестница.xlsx
+++ b/документы/замеры-объектов/2026-08-02-Евгений-замеры-санузлы-коридор-лестница.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C5ED1E-B91A-494E-8241-03F1762526BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136B1F6A-6E48-453B-B734-37823F7AA0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t xml:space="preserve">Санузел 1 </t>
   </si>
@@ -58,6 +58,12 @@
   </si>
   <si>
     <t xml:space="preserve">лестница </t>
+  </si>
+  <si>
+    <t xml:space="preserve">столешница </t>
+  </si>
+  <si>
+    <t>полы общ</t>
   </si>
 </sst>
 </file>
@@ -375,10 +381,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -391,14 +400,14 @@
       <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="M1">
-        <v>1.23</v>
-      </c>
-      <c r="N1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.34499999999999997</v>
       </c>
@@ -427,10 +436,16 @@
         <v>1.23</v>
       </c>
       <c r="N2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.34499999999999997</v>
       </c>
@@ -462,7 +477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1.4890000000000001</v>
       </c>
@@ -488,13 +503,13 @@
         <v>1.8240000000000001</v>
       </c>
       <c r="M4">
-        <v>0.46899999999999997</v>
+        <v>1.23</v>
       </c>
       <c r="N4">
-        <v>2.613</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1.4890000000000001</v>
       </c>
@@ -520,13 +535,13 @@
         <v>0.84</v>
       </c>
       <c r="M5">
-        <v>0.88</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="N5">
         <v>2.613</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1.7000000000000001E-2</v>
       </c>
@@ -555,10 +570,10 @@
         <v>0.88</v>
       </c>
       <c r="N6">
-        <v>0.46899999999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2.613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -590,7 +605,7 @@
         <v>0.46899999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -615,8 +630,14 @@
       <c r="K8">
         <v>0.315</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M8">
+        <v>0.88</v>
+      </c>
+      <c r="N8">
+        <v>0.46899999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.5</v>
       </c>
@@ -642,7 +663,7 @@
         <v>1.093</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1.0900000000000001</v>
       </c>
@@ -668,7 +689,7 @@
         <v>1.103</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2.1859999999999999</v>
       </c>
@@ -688,7 +709,7 @@
         <v>0.26200000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.5</v>
       </c>
@@ -711,7 +732,7 @@
         <v>0.26200000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.1</v>
       </c>
@@ -737,7 +758,7 @@
         <v>0.26200000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.1</v>
       </c>
@@ -763,7 +784,7 @@
         <v>0.26200000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.40200000000000002</v>
       </c>
@@ -789,7 +810,7 @@
         <v>0.26200000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2.6520000000000001</v>
       </c>
